--- a/output/graficos_nacionales/plot_nacional_serie_m_movinterna_a_2024.xlsx
+++ b/output/graficos_nacionales/plot_nacional_serie_m_movinterna_a_2024.xlsx
@@ -30,7 +30,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-20 21:40</t>
+    <t xml:space="preserve">2026-08-21 12:50</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_serie_m_movinterna_a_2024.xlsx
+++ b/output/graficos_nacionales/plot_nacional_serie_m_movinterna_a_2024.xlsx
@@ -30,7 +30,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-21 12:50</t>
+    <t xml:space="preserve">2026-09-07 12:37</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
